--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -22266,6 +22266,408 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22299,7 +22701,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22784,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -22392,7 +22794,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -22412,7 +22814,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1753,9 +1744,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2005,7 +1993,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2303,9 +2291,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2555,7 +2540,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2853,9 +2838,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3105,7 +3087,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3403,9 +3385,6 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3655,7 +3634,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -3950,9 +3929,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4491,9 +4467,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4642,9 +4615,6 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4894,7 +4864,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5041,9 +5011,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5340,9 +5307,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5592,7 +5556,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -5890,9 +5854,6 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6142,7 +6103,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6440,9 +6401,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6692,7 +6650,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6987,9 +6945,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7528,9 +7483,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7679,9 +7631,6 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7931,7 +7880,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8078,9 +8027,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8377,9 +8323,6 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8629,7 +8572,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -8927,9 +8870,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9179,7 +9119,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9477,9 +9417,6 @@
       <c r="P51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9729,7 +9666,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10027,9 +9964,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10279,7 +10213,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10426,9 +10360,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.0004682466352329422</v>
       </c>
@@ -10574,9 +10505,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11115,9 +11043,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11263,9 +11188,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11562,9 +11484,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11814,7 +11733,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12112,9 +12031,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12364,7 +12280,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -12662,9 +12578,6 @@
       <c r="P69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12914,7 +12827,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13212,9 +13125,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13464,7 +13374,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13611,9 +13521,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14152,9 +14059,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14300,9 +14204,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14599,9 +14500,6 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14851,7 +14749,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15149,9 +15047,6 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15401,7 +15296,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -15699,9 +15594,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15951,7 +15843,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16249,9 +16141,6 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16501,7 +16390,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -16799,9 +16688,6 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17051,7 +16937,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -17346,9 +17232,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17494,9 +17377,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17642,9 +17522,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17793,9 +17670,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18045,7 +17919,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -18192,9 +18066,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18343,9 +18214,6 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18595,7 +18463,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18742,9 +18610,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18893,9 +18758,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19145,7 +19007,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -19292,9 +19154,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19443,9 +19302,6 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19695,7 +19551,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -19842,9 +19698,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19990,9 +19843,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20141,9 +19991,6 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20393,7 +20240,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -20540,9 +20387,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20691,9 +20535,6 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20943,7 +20784,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -21090,9 +20931,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -21241,9 +21079,6 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21493,7 +21328,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -21640,9 +21475,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21791,9 +21623,6 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -22043,7 +21872,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -22190,9 +22019,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22341,9 +22167,6 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22593,7 +22416,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -17040,12 +17040,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17079,84 +17079,92 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>23</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.002335598481789786</v>
+        <v>0</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17183,17 +17191,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17232,76 +17240,165 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary human rabies notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17333,12 +17430,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17372,13 +17469,16 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>23</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.002335598481789786</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17411,42 +17511,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17478,12 +17578,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17508,7 +17608,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17556,42 +17656,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17623,12 +17723,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17653,7 +17753,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17667,9 +17767,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17678,82 +17775,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17780,17 +17863,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17815,7 +17898,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -17829,168 +17912,76 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18022,12 +18013,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18052,7 +18043,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -18066,6 +18057,9 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18074,68 +18068,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18162,7 +18170,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18197,7 +18205,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -18214,23 +18222,98 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -18324,17 +18407,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18359,7 +18442,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -18373,168 +18456,76 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18566,12 +18557,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18596,7 +18587,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -18610,6 +18601,9 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18618,68 +18612,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18706,7 +18714,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -18741,7 +18749,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18758,23 +18766,98 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -18868,17 +18951,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18903,7 +18986,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18917,168 +19000,76 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19110,12 +19101,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19140,7 +19131,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19154,6 +19145,9 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19162,68 +19156,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19258,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -19285,7 +19293,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19302,23 +19310,98 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -19412,17 +19495,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19447,7 +19530,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19461,168 +19544,76 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19654,12 +19645,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19684,12 +19675,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -19698,6 +19689,9 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19706,68 +19700,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19794,17 +19802,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19829,12 +19837,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -19843,76 +19851,168 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19944,12 +20044,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19974,7 +20074,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19988,9 +20088,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19999,82 +20096,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20101,17 +20184,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20136,7 +20219,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -20150,168 +20233,76 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20343,12 +20334,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20373,7 +20364,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20387,6 +20378,9 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20395,68 +20389,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20483,7 +20491,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -20518,7 +20526,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20535,23 +20543,98 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -20645,17 +20728,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20680,7 +20763,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20694,168 +20777,76 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN115" t="b">
-        <v>1</v>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20887,12 +20878,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20917,7 +20908,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20931,6 +20922,9 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20939,68 +20933,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21035,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -21062,7 +21070,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -21079,23 +21087,98 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -21189,17 +21272,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21224,7 +21307,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21238,168 +21321,76 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21422,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21461,7 +21452,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21475,6 +21466,9 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21483,68 +21477,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21571,7 +21579,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21606,7 +21614,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21623,23 +21631,98 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -21733,17 +21816,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21768,7 +21851,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21782,168 +21865,76 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21975,12 +21966,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -22005,12 +21996,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -22019,6 +22010,9 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22027,68 +22021,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22115,7 +22123,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -22150,12 +22158,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -22167,23 +22175,98 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -22277,215 +22360,522 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>狂犬病</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="inlineStr">
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
+      <c r="V126" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="W124" t="inlineStr">
+      <c r="W126" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
+      <c r="AB126" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
+      <c r="AC126" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD124" t="inlineStr">
+      <c r="AD126" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr">
+      <c r="AE126" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF124" t="inlineStr">
+      <c r="AF126" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG124" t="inlineStr">
+      <c r="AG126" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH124" t="inlineStr">
+      <c r="AH126" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI124" t="inlineStr">
+      <c r="AI126" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ124" t="inlineStr">
+      <c r="AJ126" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
-      <c r="AK124" t="inlineStr">
+      <c r="AK126" t="inlineStr">
         <is>
           <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
+      <c r="AM126" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN124" t="b">
+      <c r="AN126" t="b">
         <v>1</v>
       </c>
-      <c r="AO124" t="inlineStr">
+      <c r="AO126" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP124" t="inlineStr">
+      <c r="AP126" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ124" t="inlineStr">
+      <c r="AQ126" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS124" t="inlineStr">
+      <c r="AS126" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="AT124" t="n">
+      <c r="AT126" t="n">
         <v>1</v>
       </c>
-      <c r="AU124" t="inlineStr">
+      <c r="AU126" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV124" t="inlineStr">
+      <c r="AV126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AW126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr">
+      <c r="AY126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA124" t="inlineStr">
+      <c r="BA126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB124" t="inlineStr">
+      <c r="BB126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC124" t="inlineStr">
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22607,7 +22997,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -22617,7 +23007,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -22637,7 +23027,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -22881,6 +22881,405 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22914,7 +23313,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -22997,7 +23396,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -23007,7 +23406,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -23027,7 +23426,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -20044,12 +20044,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20083,13 +20083,16 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>37</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.002477149904928561</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20122,42 +20125,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20189,12 +20192,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20219,7 +20222,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -20267,42 +20270,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20334,12 +20337,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20364,7 +20367,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20378,9 +20381,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20389,82 +20389,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20491,7 +20477,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -20543,98 +20529,23 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -20728,17 +20639,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20763,7 +20674,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20777,76 +20688,168 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>1</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20878,12 +20881,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20908,7 +20911,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20922,9 +20925,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20933,82 +20933,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21021,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -21087,98 +21073,23 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -21272,17 +21183,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21307,7 +21218,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21321,76 +21232,168 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21425,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21452,7 +21455,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21466,9 +21469,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21477,82 +21477,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21565,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21631,98 +21617,23 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -21816,17 +21727,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21851,7 +21762,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21865,76 +21776,168 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21966,12 +21969,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21996,7 +21999,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -22010,9 +22013,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22021,82 +22021,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22123,7 +22109,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -22175,98 +22161,23 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -22360,17 +22271,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22395,12 +22306,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -22409,76 +22320,168 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22510,12 +22513,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22540,7 +22543,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22554,9 +22557,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22565,82 +22565,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22653,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22719,98 +22705,23 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22904,7 +22815,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -22939,7 +22850,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22956,23 +22867,98 @@
       <c r="P127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -23066,7 +23052,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -23118,98 +23104,23 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -23275,6 +23186,243 @@
         </is>
       </c>
       <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23396,7 +23544,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -23406,7 +23554,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -23458,7 +23606,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -23468,7 +23616,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>125</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -23428,6 +23428,405 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23461,7 +23860,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -23544,7 +23943,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -23554,7 +23953,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -23574,7 +23973,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -20192,12 +20192,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20270,42 +20270,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20337,12 +20337,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20415,42 +20415,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20482,12 +20482,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20526,9 +20526,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20537,82 +20534,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20622,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -20691,98 +20674,23 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN115" t="b">
-        <v>1</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -20876,17 +20784,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20911,7 +20819,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20925,76 +20833,168 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21026,12 +21026,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -21070,9 +21070,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21081,82 +21078,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21166,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -21235,98 +21218,23 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21420,17 +21328,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21455,7 +21363,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21469,76 +21377,168 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21570,12 +21570,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21614,9 +21614,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21625,82 +21622,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21727,7 +21710,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -21779,98 +21762,23 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -21964,17 +21872,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21999,7 +21907,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -22013,76 +21921,168 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22114,12 +22114,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -22158,9 +22158,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22169,82 +22166,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22254,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -22323,98 +22306,23 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -22508,17 +22416,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22543,12 +22451,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -22557,76 +22465,168 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22658,12 +22658,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22702,9 +22702,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -22713,82 +22710,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22815,7 +22798,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -22867,98 +22850,23 @@
       <c r="P127" t="n">
         <v>0</v>
       </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -23052,7 +22960,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -23087,7 +22995,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -23104,23 +23012,98 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -23214,7 +23197,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -23266,98 +23249,23 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23451,7 +23359,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -23486,7 +23394,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -23503,23 +23411,98 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -23613,7 +23596,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -23665,98 +23648,23 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -23822,6 +23730,243 @@
         </is>
       </c>
       <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23943,7 +24088,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -23953,7 +24098,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -23972,6 +23972,550 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24005,7 +24549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -24098,7 +24642,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -24118,7 +24662,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
